--- a/tests/v1/fixtures/office6m/2026-10/bank_statements/HB_HOLD_USD_2026-10_mtd.xlsx
+++ b/tests/v1/fixtures/office6m/2026-10/bank_statements/HB_HOLD_USD_2026-10_mtd.xlsx
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>596959.9</v>
+        <v>723709.9</v>
       </c>
       <c r="E2" t="n">
-        <v>433055.94</v>
+        <v>306305.94</v>
       </c>
       <c r="F2" t="n">
         <v>1030015.84</v>
